--- a/lab 3/Book1.xlsx
+++ b/lab 3/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dasha/projects/DataScience_2026/lab 3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3817B456-BDAA-9046-8933-FE3540830ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6F4C76-7395-344C-B2B1-F8F413FFE14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9200" yWindow="1880" windowWidth="18540" windowHeight="14160" xr2:uid="{DB472C67-76D7-754A-A5E7-8EF10A6A09DC}"/>
+    <workbookView xWindow="9080" yWindow="7780" windowWidth="18540" windowHeight="9300" xr2:uid="{DB472C67-76D7-754A-A5E7-8EF10A6A09DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,47 +67,47 @@
     <t>Критерій 10</t>
   </si>
   <si>
-    <t>Товар 1</t>
-  </si>
-  <si>
-    <t>Товар 2</t>
-  </si>
-  <si>
-    <t>Товар 3</t>
-  </si>
-  <si>
-    <t>Товар 4</t>
-  </si>
-  <si>
-    <t>Товар 5</t>
-  </si>
-  <si>
-    <t>Товар 6</t>
-  </si>
-  <si>
-    <t>Товар 7</t>
-  </si>
-  <si>
-    <t>Товар 8</t>
-  </si>
-  <si>
-    <t>Товар 9</t>
-  </si>
-  <si>
-    <t>Товар 10</t>
-  </si>
-  <si>
     <t>макс</t>
   </si>
   <si>
     <t>мін</t>
+  </si>
+  <si>
+    <t>Товар1</t>
+  </si>
+  <si>
+    <t>Товар2</t>
+  </si>
+  <si>
+    <t>Товар3</t>
+  </si>
+  <si>
+    <t>Товар4</t>
+  </si>
+  <si>
+    <t>Товар5</t>
+  </si>
+  <si>
+    <t>Товар6</t>
+  </si>
+  <si>
+    <t>Товар7</t>
+  </si>
+  <si>
+    <t>Товар8</t>
+  </si>
+  <si>
+    <t>Товар9</t>
+  </si>
+  <si>
+    <t>Товар10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -134,13 +134,43 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7E79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5FC79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -155,18 +185,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFD5FC79"/>
+      <color rgb="FFFF7E79"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -480,34 +532,34 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -520,10 +572,10 @@
       <c r="C2" s="1">
         <v>749</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="7">
         <v>1099</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="6">
         <v>349</v>
       </c>
       <c r="F2" s="1">
@@ -535,17 +587,17 @@
       <c r="H2" s="1">
         <v>599</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="8">
         <v>279</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="7">
         <v>1199</v>
       </c>
       <c r="K2" s="1">
         <v>449</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -558,10 +610,10 @@
       <c r="C3" s="1">
         <v>195</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="6">
         <v>174</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="7">
         <v>210</v>
       </c>
       <c r="F3" s="1">
@@ -573,17 +625,17 @@
       <c r="H3" s="1">
         <v>202</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="7">
         <v>215</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="8">
         <v>170</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="6">
         <v>175</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -596,10 +648,10 @@
       <c r="C4" s="1">
         <v>8.1</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="6">
         <v>6.9</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="7">
         <v>9.1999999999999993</v>
       </c>
       <c r="F4" s="1">
@@ -611,17 +663,17 @@
       <c r="H4" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="7">
         <v>9.5</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="8">
         <v>6.5</v>
       </c>
       <c r="K4" s="1">
         <v>7.2</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -634,10 +686,10 @@
       <c r="C5" s="1">
         <v>90</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="6">
         <v>65</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="7">
         <v>110</v>
       </c>
       <c r="F5" s="1">
@@ -649,33 +701,33 @@
       <c r="H5" s="1">
         <v>95</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="7">
         <v>120</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="8">
         <v>60</v>
       </c>
       <c r="K5" s="1">
         <v>85</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="6">
         <v>38</v>
       </c>
       <c r="C6" s="1">
         <v>41</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="6">
         <v>36</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="7">
         <v>45</v>
       </c>
       <c r="F6" s="1">
@@ -687,17 +739,17 @@
       <c r="H6" s="1">
         <v>42</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="7">
         <v>46</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="8">
         <v>35</v>
       </c>
       <c r="K6" s="1">
         <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -710,32 +762,32 @@
       <c r="C7" s="1">
         <v>5</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="7">
         <v>6</v>
       </c>
       <c r="F7" s="1">
         <v>5.5</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="6">
         <v>4.2</v>
       </c>
       <c r="H7" s="1">
         <v>5.2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="7">
         <v>6.5</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="8">
         <v>3.8</v>
       </c>
       <c r="K7" s="1">
         <v>4.8</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -748,10 +800,10 @@
       <c r="C8" s="1">
         <v>105</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="7">
         <v>150</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="6">
         <v>60</v>
       </c>
       <c r="F8" s="1">
@@ -763,17 +815,17 @@
       <c r="H8" s="1">
         <v>90</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="8">
         <v>50</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="7">
         <v>160</v>
       </c>
       <c r="K8" s="1">
         <v>75</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -786,7 +838,7 @@
       <c r="C9" s="1">
         <v>44</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="6">
         <v>40</v>
       </c>
       <c r="E9" s="1">
@@ -795,23 +847,23 @@
       <c r="F9" s="1">
         <v>46</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="6">
         <v>41</v>
       </c>
       <c r="H9" s="1">
         <v>45</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="7">
         <v>50</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="8">
         <v>39</v>
       </c>
       <c r="K9" s="1">
         <v>43</v>
       </c>
-      <c r="L9" t="s">
-        <v>21</v>
+      <c r="L9" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -824,13 +876,13 @@
       <c r="C10" s="1">
         <v>4200</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="7">
         <v>5000</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="6">
         <v>3500</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="6">
         <v>3800</v>
       </c>
       <c r="G10" s="1">
@@ -842,14 +894,14 @@
       <c r="I10" s="1">
         <v>3200</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="9">
         <v>5200</v>
       </c>
       <c r="K10" s="1">
         <v>4100</v>
       </c>
-      <c r="L10" t="s">
-        <v>20</v>
+      <c r="L10" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -862,10 +914,10 @@
       <c r="C11" s="1">
         <v>8.4</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="7">
         <v>9.5</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="6">
         <v>7.2</v>
       </c>
       <c r="F11" s="1">
@@ -877,21 +929,22 @@
       <c r="H11" s="1">
         <v>8.1</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="6">
         <v>6.8</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="9">
         <v>9.6999999999999993</v>
       </c>
       <c r="K11" s="1">
         <v>8.3000000000000007</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>